--- a/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
+++ b/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="38">
   <si>
     <t>Result</t>
   </si>
@@ -109,6 +109,45 @@
   </si>
   <si>
     <t>Sat Oct 04 16:19:51 EDT 2025</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:53:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:53:42 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:53:51 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 16:54:01 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 18:26:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 14 18:26:32 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:17:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 22:17:41 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:14:18 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:14:27 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:14:36 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu May 21 23:14:44 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -515,7 +554,7 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -532,7 +571,7 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -549,7 +588,7 @@
         <v>5</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -566,7 +605,7 @@
         <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>

--- a/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
+++ b/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="46">
   <si>
     <t>Result</t>
   </si>
@@ -148,6 +148,30 @@
   </si>
   <si>
     <t>Thu May 21 23:14:44 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:03:39 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:03:48 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:03:57 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jun 25 00:04:05 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:01:21 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:01:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:01:38 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Jul 09 23:01:47 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -521,7 +545,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F89B3EE-CDFD-48C7-AA85-7D2CDFC70A3F}">
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:E7"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.453125" collapsed="true"/>
@@ -550,11 +574,11 @@
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
+      <c r="A2" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="B2" t="s">
-        <v>34</v>
+      <c r="B2" t="s" s="1">
+        <v>42</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -567,11 +591,11 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+      <c r="A3" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="B3" t="s">
-        <v>35</v>
+      <c r="B3" t="s" s="1">
+        <v>43</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -584,11 +608,11 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+      <c r="A4" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="B4" t="s">
-        <v>36</v>
+      <c r="B4" t="s" s="1">
+        <v>44</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -601,11 +625,11 @@
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+      <c r="A5" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="B5" t="s">
-        <v>37</v>
+      <c r="B5" t="s" s="1">
+        <v>45</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -618,10 +642,10 @@
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+      <c r="A6" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" t="s" s="1">
         <v>17</v>
       </c>
       <c r="C6" s="1" t="s">
@@ -635,10 +659,10 @@
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
+      <c r="A7" t="s" s="1">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" t="s" s="1">
         <v>18</v>
       </c>
       <c r="C7" s="1" t="s">

--- a/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
+++ b/KatalonData/RADTestData/TaxPayerSSNNoMatch.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\t465179\Documents\git\VPS-Katalon\VPS-Katalon\KatalonData\RADTestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr documentId="13_ncr:1_{3E8D6EC3-01A7-40BE-BBB5-EA35CED4B9D1}" revIDLastSave="0" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0959697-3CFB-4660-AF6F-116AF64A4D3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowHeight="15840" windowWidth="29040" xWindow="28680" xr2:uid="{64AAF6A4-B582-41C3-B2B7-EAC922D4E6FB}" yWindow="-3945"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{64AAF6A4-B582-41C3-B2B7-EAC922D4E6FB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId1" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="20">
   <si>
     <t>Result</t>
   </si>
@@ -75,93 +75,9 @@
     <t>Existing Liability with Notice/Invoice Number</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:03:22 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:03:37 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:03:51 EST 2025</t>
-  </si>
-  <si>
-    <t>Mon Feb 24 23:04:06 EST 2025</t>
-  </si>
-  <si>
     <t>Mon Feb 24 23:04:21 EST 2025</t>
   </si>
   <si>
-    <t>Mon Feb 24 23:04:35 EST 2025</t>
-  </si>
-  <si>
-    <t>DoNotRun</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:19:28 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:19:35 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:19:43 EDT 2025</t>
-  </si>
-  <si>
-    <t>Sat Oct 04 16:19:51 EDT 2025</t>
-  </si>
-  <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:53:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:53:42 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:53:51 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 16:54:01 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 18:26:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 14 18:26:32 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:17:29 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 22:17:41 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:14:18 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:14:27 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:14:36 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu May 21 23:14:44 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:03:39 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:03:48 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:03:57 EDT 2026</t>
-  </si>
-  <si>
-    <t>Thu Jun 25 00:04:05 EDT 2026</t>
-  </si>
-  <si>
     <t>Thu Jul 09 23:01:21 EDT 2026</t>
   </si>
   <si>
@@ -172,13 +88,18 @@
   </si>
   <si>
     <t>Thu Jul 09 23:01:47 EDT 2026</t>
+  </si>
+  <si>
+    <t>DONOTRUN</t>
+  </si>
+  <si>
+    <t>Wed Aug 05 11:49:31 EDT 2026</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -221,22 +142,22 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
-    <xf applyAlignment="1" applyBorder="1" borderId="1" fillId="0" fontId="0" numFmtId="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" applyBorder="1" applyNumberFormat="1" borderId="1" fillId="0" fontId="0" numFmtId="49" xfId="0">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium2"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -253,10 +174,10 @@
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="44546A"/>
@@ -291,7 +212,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
-        <a:latin panose="020F0302020204030204" typeface="Calibri Light"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック Light"/>
@@ -343,7 +264,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin panose="020F0502020204030204" typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="游ゴシック"/>
@@ -454,21 +375,21 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="6350">
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="12700">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
           <a:miter lim="800000"/>
         </a:ln>
-        <a:ln algn="ctr" cap="flat" cmpd="sng" w="19050">
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -485,7 +406,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw algn="ctr" blurRad="57150" dir="5400000" dist="19050" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="63000"/>
               </a:srgbClr>
@@ -537,26 +458,26 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" name="Office 2013 - 2022 Theme" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F89B3EE-CDFD-48C7-AA85-7D2CDFC70A3F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F89B3EE-CDFD-48C7-AA85-7D2CDFC70A3F}">
   <dimension ref="A1:E7"/>
-  <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.19921875" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="7.453125" collapsed="true"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="26.453125" collapsed="true"/>
-    <col min="3" max="3" customWidth="true" style="1" width="15.453125" collapsed="true"/>
-    <col min="4" max="4" customWidth="true" style="1" width="50.81640625" collapsed="true"/>
-    <col min="5" max="5" customWidth="true" style="1" width="34.453125" collapsed="true"/>
-    <col min="6" max="16384" style="1" width="9.1796875" collapsed="true"/>
+    <col min="1" max="1" width="7.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="2" max="2" width="26.46484375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
+    <col min="3" max="3" width="15.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="4" max="4" width="50.796875" style="1" customWidth="1" collapsed="1"/>
+    <col min="5" max="5" width="34.46484375" style="1" customWidth="1" collapsed="1"/>
+    <col min="6" max="16384" width="9.19921875" style="1" collapsed="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -573,12 +494,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A2" t="s" s="1">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B2" t="s" s="1">
-        <v>42</v>
+      <c r="B2" s="1" t="s">
+        <v>14</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>4</v>
@@ -590,12 +511,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A3" t="s" s="1">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" t="s" s="1">
-        <v>43</v>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>4</v>
@@ -607,12 +528,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A4" t="s" s="1">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A4" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="s" s="1">
-        <v>44</v>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>4</v>
@@ -624,12 +545,12 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A5" t="s" s="1">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B5" t="s" s="1">
-        <v>45</v>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>4</v>
@@ -641,15 +562,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A6" t="s" s="1">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B6" t="s" s="1">
-        <v>17</v>
+      <c r="B6" s="1" t="s">
+        <v>13</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>12</v>
@@ -658,15 +579,15 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A7" t="s" s="1">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
+      <c r="A7" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B7" t="s" s="1">
-        <v>18</v>
+      <c r="B7" s="1" t="s">
+        <v>19</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>7</v>
@@ -676,8 +597,8 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-  <pageSetup horizontalDpi="4294967293" orientation="portrait" r:id="rId1" verticalDpi="0"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967293" verticalDpi="0" r:id="rId1"/>
   <headerFooter>
     <oddFooter xml:space="preserve">&amp;C_x000D_&amp;1#&amp;"Calibri"&amp;10&amp;K000000 Public </oddFooter>
   </headerFooter>
